--- a/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
@@ -110,10 +110,10 @@
     <t>high_school_biology</t>
   </si>
   <si>
-    <t>39.199999999999996</t>
-  </si>
-  <si>
-    <t>110.79999999999997</t>
+    <t>39.099999999999994</t>
+  </si>
+  <si>
+    <t>112.89999999999999</t>
   </si>
   <si>
     <t>high_school_biology first 100</t>
@@ -1896,13 +1896,13 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K34" s="2">
-        <v>-32.6</v>
+        <v>-32.1999999999999</v>
       </c>
     </row>
     <row r="35" spans="4:11">
@@ -1919,13 +1919,13 @@
         <v>22</v>
       </c>
       <c r="I35">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K35" s="2">
-        <v>-56.2</v>
+        <v>-56.3</v>
       </c>
     </row>
     <row r="37" spans="1:1">

--- a/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
   <si>
     <t>problem set size</t>
   </si>
@@ -77,6 +77,15 @@
     <t>college_biology</t>
   </si>
   <si>
+    <t>bm160</t>
+  </si>
+  <si>
+    <t>bm140</t>
+  </si>
+  <si>
+    <t>18.499999999999996</t>
+  </si>
+  <si>
     <t>45.49999999999999</t>
   </si>
   <si>
@@ -105,6 +114,9 @@
   </si>
   <si>
     <t>55.99999999999999</t>
+  </si>
+  <si>
+    <t>62.300000000000004</t>
   </si>
   <si>
     <t>high_school_biology</t>
@@ -1294,7 +1306,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="35.3653846153846" customWidth="1"/>
@@ -1468,603 +1480,663 @@
     </row>
     <row r="11" spans="4:11">
       <c r="D11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>14112</v>
+        <v>16144</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H11">
         <v>11</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J11" s="2">
-        <v>34.2</v>
+        <v>24.9</v>
       </c>
       <c r="K11" s="2">
-        <v>-20.5</v>
+        <v>-3.69999999999999</v>
       </c>
     </row>
     <row r="12" spans="4:11">
       <c r="D12" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E12">
-        <v>12015</v>
+        <v>15497</v>
       </c>
       <c r="G12" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H12">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I12">
-        <v>12</v>
-      </c>
-      <c r="J12" s="2">
-        <v>36.9</v>
+        <v>11</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K12" s="2">
-        <v>-32.9</v>
+        <v>-10.5999999999999</v>
       </c>
     </row>
     <row r="13" spans="4:11">
       <c r="D13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>7435</v>
+        <v>14112</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I13">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="J13" s="2">
+        <v>34.2</v>
       </c>
       <c r="K13" s="2">
-        <v>-20.9999999999999</v>
+        <v>-20.5</v>
       </c>
     </row>
     <row r="14" spans="4:11">
       <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>12015</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <v>12</v>
+      </c>
+      <c r="J14" s="2">
+        <v>36.9</v>
+      </c>
+      <c r="K14" s="2">
+        <v>-32.9</v>
+      </c>
+    </row>
+    <row r="15" spans="4:11">
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15">
+        <v>7435</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15">
+        <v>15</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="2">
+        <v>-20.9999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="4:11">
+      <c r="D16" t="s">
         <v>13</v>
       </c>
-      <c r="E14">
+      <c r="E16">
         <v>679</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G16" t="s">
         <v>13</v>
       </c>
-      <c r="H14">
+      <c r="H16">
         <v>19</v>
       </c>
-      <c r="I14">
+      <c r="I16">
         <v>14</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J16" s="2">
         <v>78.8</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K16" s="2">
         <v>-49.4</v>
       </c>
     </row>
-    <row r="15" ht="14" customHeight="1"/>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" t="s">
+    <row r="17" ht="14" customHeight="1"/>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
-      <c r="B17">
+    <row r="19" spans="2:11">
+      <c r="B19">
         <v>225</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D19" t="s">
         <v>4</v>
       </c>
-      <c r="E17">
+      <c r="E19">
         <v>22475</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H19" t="s">
         <v>5</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I19" t="s">
         <v>6</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J19" t="s">
         <v>7</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K19" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="4:11">
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18">
-        <v>21961</v>
-      </c>
-      <c r="G18" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18">
-        <v>3</v>
-      </c>
-      <c r="I18">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" s="1">
-        <v>-12.7999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="4:11">
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19">
-        <v>20804</v>
-      </c>
-      <c r="G19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19">
-        <v>3</v>
-      </c>
-      <c r="I19">
-        <v>9</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="1">
-        <v>-20.9999999999999</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E20">
-        <v>16174</v>
+        <v>21961</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20">
         <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="1">
-        <v>-32.5</v>
+        <v>-12.7999999999999</v>
       </c>
     </row>
     <row r="21" spans="4:11">
       <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21">
+        <v>20804</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>9</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="1">
+        <v>-20.9999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="4:11">
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22">
+        <v>16174</v>
+      </c>
+      <c r="G22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="1">
+        <v>-32.5</v>
+      </c>
+    </row>
+    <row r="23" spans="4:11">
+      <c r="D23" t="s">
         <v>13</v>
       </c>
-      <c r="E21">
+      <c r="E23">
         <v>1170</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G23" t="s">
         <v>13</v>
       </c>
-      <c r="H21">
+      <c r="H23">
         <v>9</v>
       </c>
-      <c r="I21">
+      <c r="I23">
         <v>11</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J23" s="2">
         <v>38.4</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K23" s="2">
         <v>-29.7</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="2:11">
-      <c r="B24">
+    <row r="26" spans="2:11">
+      <c r="B26">
         <v>139</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D26" t="s">
         <v>4</v>
       </c>
-      <c r="E24">
+      <c r="E26">
         <v>13791</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H26" t="s">
         <v>5</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I26" t="s">
         <v>6</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J26" t="s">
         <v>7</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K26" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="4:11">
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25">
-        <v>12996</v>
-      </c>
-      <c r="G25" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25">
-        <v>15</v>
-      </c>
-      <c r="I25">
-        <v>16</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="1">
-        <v>-14.7</v>
-      </c>
-    </row>
-    <row r="26" spans="4:11">
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26">
-        <v>11284</v>
-      </c>
-      <c r="G26" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26">
-        <v>15</v>
-      </c>
-      <c r="I26">
-        <v>19</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" s="1">
-        <v>-41.3999999999999</v>
       </c>
     </row>
     <row r="27" spans="4:11">
       <c r="D27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E27">
-        <v>7562</v>
+        <v>12996</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H27">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I27">
-        <v>18</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" s="2">
-        <v>-34.7999999999999</v>
+        <v>16</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" s="1">
+        <v>-14.7</v>
       </c>
     </row>
     <row r="28" spans="4:11">
       <c r="D28" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <v>700</v>
+        <v>11284</v>
       </c>
       <c r="G28" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>15</v>
       </c>
       <c r="I28">
+        <v>19</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="K28" s="1">
+        <v>-41.3999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="4:11">
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29">
+        <v>7562</v>
+      </c>
+      <c r="G29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29">
+        <v>20</v>
+      </c>
+      <c r="I29">
+        <v>18</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29" s="2">
+        <v>-34.7999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="4:11">
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <v>700</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>15</v>
+      </c>
+      <c r="I30">
+        <v>26</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" s="1">
         <v>-92.4999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" t="s">
+    <row r="31" spans="8:11">
+      <c r="H31">
+        <v>12</v>
+      </c>
+      <c r="I31">
+        <v>29</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="1">
+        <v>-84.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
-      <c r="B31">
+    <row r="33" spans="2:11">
+      <c r="B33">
         <v>347</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" t="s">
         <v>4</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <v>34556</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H33" t="s">
         <v>5</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I33" t="s">
         <v>6</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J33" t="s">
         <v>7</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K33" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="4:11">
-      <c r="D32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32">
-        <v>26342</v>
-      </c>
-      <c r="G32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32">
-        <v>8</v>
-      </c>
-      <c r="I32">
-        <v>11</v>
-      </c>
-      <c r="J32" s="1">
-        <v>21.7</v>
-      </c>
-      <c r="K32" s="1">
-        <v>-35</v>
-      </c>
-    </row>
-    <row r="33" spans="4:11">
-      <c r="D33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33">
-        <v>18391</v>
-      </c>
-      <c r="G33" t="s">
-        <v>10</v>
-      </c>
-      <c r="H33">
-        <v>9</v>
-      </c>
-      <c r="I33">
-        <v>12</v>
-      </c>
-      <c r="J33" s="1">
-        <v>29.1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>-44.9999999999999</v>
       </c>
     </row>
     <row r="34" spans="4:11">
       <c r="D34" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E34">
-        <v>9974</v>
+        <v>26342</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>10</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K34" s="2">
-        <v>-32.1999999999999</v>
+        <v>11</v>
+      </c>
+      <c r="J34" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="K34" s="1">
+        <v>-35</v>
       </c>
     </row>
     <row r="35" spans="4:11">
       <c r="D35" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35">
+        <v>18391</v>
+      </c>
+      <c r="G35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35">
+        <v>9</v>
+      </c>
+      <c r="I35">
+        <v>12</v>
+      </c>
+      <c r="J35" s="1">
+        <v>29.1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>-44.9999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="4:11">
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36">
+        <v>9974</v>
+      </c>
+      <c r="G36" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36">
+        <v>9</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36" s="2">
+        <v>-32.1999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="4:11">
+      <c r="D37" t="s">
         <v>13</v>
       </c>
-      <c r="E35">
+      <c r="E37">
         <v>715</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G37" t="s">
         <v>13</v>
       </c>
-      <c r="H35">
+      <c r="H37">
         <v>22</v>
       </c>
-      <c r="I35">
+      <c r="I37">
         <v>11</v>
       </c>
-      <c r="J35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K35" s="2">
+      <c r="J37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37" s="2">
         <v>-56.3</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="8:11">
-      <c r="H38" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="8:11">
+      <c r="H40" t="s">
         <v>5</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I40" t="s">
         <v>6</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J40" t="s">
         <v>7</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K40" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="7:11">
-      <c r="G39" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39">
-        <v>9</v>
-      </c>
-      <c r="I39">
-        <v>8</v>
-      </c>
-      <c r="J39" s="1">
-        <v>14.1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>-30.7999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="7:11">
-      <c r="G40" t="s">
-        <v>30</v>
-      </c>
-      <c r="H40">
-        <v>13</v>
-      </c>
-      <c r="I40">
-        <v>10</v>
-      </c>
-      <c r="J40" s="1">
-        <v>21.0999999999999</v>
-      </c>
-      <c r="K40" s="1">
-        <v>-32.2</v>
       </c>
     </row>
     <row r="41" spans="7:11">
       <c r="G41" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H41">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I41">
         <v>8</v>
       </c>
       <c r="J41" s="1">
+        <v>14.1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>-30.7999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="7:11">
+      <c r="G42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42">
+        <v>13</v>
+      </c>
+      <c r="I42">
+        <v>10</v>
+      </c>
+      <c r="J42" s="1">
+        <v>21.0999999999999</v>
+      </c>
+      <c r="K42" s="1">
+        <v>-32.2</v>
+      </c>
+    </row>
+    <row r="43" spans="7:11">
+      <c r="G43" t="s">
+        <v>35</v>
+      </c>
+      <c r="H43">
+        <v>16</v>
+      </c>
+      <c r="I43">
+        <v>8</v>
+      </c>
+      <c r="J43" s="1">
         <v>21.5999999999999</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K43" s="1">
         <v>-29.2</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="8:11">
-      <c r="H44" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="8:11">
+      <c r="H46" t="s">
         <v>5</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I46" t="s">
         <v>6</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J46" t="s">
         <v>7</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K46" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="7:11">
-      <c r="G45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H45">
-        <v>4</v>
-      </c>
-      <c r="I45">
-        <v>5</v>
-      </c>
-      <c r="J45" s="1">
-        <v>2.09999999999999</v>
-      </c>
-      <c r="K45" s="1">
-        <v>-3.29999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="7:11">
-      <c r="G46" t="s">
-        <v>10</v>
-      </c>
-      <c r="H46">
-        <v>3</v>
-      </c>
-      <c r="I46">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1.59999999999999</v>
-      </c>
-      <c r="K46" s="1">
-        <v>-3.79999999999999</v>
       </c>
     </row>
     <row r="47" spans="7:11">
       <c r="G47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47">
+        <v>4</v>
+      </c>
+      <c r="I47">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
+        <v>2.09999999999999</v>
+      </c>
+      <c r="K47" s="1">
+        <v>-3.29999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="7:11">
+      <c r="G48" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48">
+        <v>3</v>
+      </c>
+      <c r="I48">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1.59999999999999</v>
+      </c>
+      <c r="K48" s="1">
+        <v>-3.79999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="7:11">
+      <c r="G49" t="s">
         <v>13</v>
       </c>
-      <c r="H47">
+      <c r="H49">
         <v>11</v>
       </c>
-      <c r="I47">
+      <c r="I49">
         <v>9</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J49" s="1">
         <v>50.8</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K49" s="1">
         <v>-28.5</v>
       </c>
     </row>

--- a/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28760" windowHeight="15300"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -145,18 +145,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -620,152 +626,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -774,6 +780,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1306,13 +1315,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K49"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr defaultColWidth="9.22727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="35.3653846153846" customWidth="1"/>
-    <col min="8" max="8" width="11.0769230769231" customWidth="1"/>
-    <col min="9" max="9" width="13.2307692307692" customWidth="1"/>
-    <col min="10" max="10" width="20.2307692307692" customWidth="1"/>
+    <col min="1" max="1" width="35.3636363636364" customWidth="1"/>
+    <col min="8" max="8" width="11.0727272727273" customWidth="1"/>
+    <col min="9" max="9" width="13.2272727272727" customWidth="1"/>
+    <col min="10" max="10" width="20.2272727272727" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1394,7 +1403,7 @@
       <c r="I5">
         <v>7</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="1">
@@ -1440,7 +1449,7 @@
       <c r="I7">
         <v>7</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="K7" s="2">
@@ -1517,14 +1526,14 @@
       <c r="I12">
         <v>11</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K12" s="2">
         <v>-10.5999999999999</v>
       </c>
     </row>
-    <row r="13" spans="4:11">
+    <row r="13" spans="4:15">
       <c r="D13" t="s">
         <v>9</v>
       </c>
@@ -1545,6 +1554,18 @@
       </c>
       <c r="K13" s="2">
         <v>-20.5</v>
+      </c>
+      <c r="L13" s="3">
+        <v>8</v>
+      </c>
+      <c r="M13" s="3">
+        <v>11</v>
+      </c>
+      <c r="N13" s="3">
+        <v>30.2999999999999</v>
+      </c>
+      <c r="O13">
+        <v>-6.4</v>
       </c>
     </row>
     <row r="14" spans="4:11">
@@ -1586,7 +1607,7 @@
       <c r="I15">
         <v>10</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="2">
@@ -1616,7 +1637,7 @@
         <v>-49.4</v>
       </c>
     </row>
-    <row r="17" ht="14" customHeight="1"/>
+    <row r="17" customHeight="1"/>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>20</v>
@@ -1664,7 +1685,7 @@
       <c r="I20">
         <v>8</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K20" s="1">
@@ -1687,7 +1708,7 @@
       <c r="I21">
         <v>9</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="4" t="s">
         <v>22</v>
       </c>
       <c r="K21" s="1">
@@ -1710,7 +1731,7 @@
       <c r="I22">
         <v>8</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="K22" s="1">
@@ -1787,7 +1808,7 @@
       <c r="I27">
         <v>16</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="J27" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K27" s="1">
@@ -1810,7 +1831,7 @@
       <c r="I28">
         <v>19</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K28" s="1">
@@ -1833,7 +1854,7 @@
       <c r="I29">
         <v>18</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K29" s="2">
@@ -1856,7 +1877,7 @@
       <c r="I30">
         <v>26</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="J30" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K30" s="1">
@@ -1870,7 +1891,7 @@
       <c r="I31">
         <v>29</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K31" s="1">
@@ -1970,7 +1991,7 @@
       <c r="I36">
         <v>10</v>
       </c>
-      <c r="J36" s="4" t="s">
+      <c r="J36" s="5" t="s">
         <v>31</v>
       </c>
       <c r="K36" s="2">
@@ -1993,7 +2014,7 @@
       <c r="I37">
         <v>11</v>
       </c>
-      <c r="J37" s="4" t="s">
+      <c r="J37" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K37" s="2">

--- a/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="37">
   <si>
     <t>problem set size</t>
   </si>
@@ -1863,7 +1863,10 @@
         <v>-92.4999999999999</v>
       </c>
     </row>
-    <row r="31" spans="8:11">
+    <row r="31" spans="7:11">
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
       <c r="H31">
         <v>12</v>
       </c>

--- a/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="40">
   <si>
     <t>problem set size</t>
   </si>
@@ -101,6 +101,12 @@
     <t>2.5000000000000004</t>
   </si>
   <si>
+    <t>high_school_geography_02</t>
+  </si>
+  <si>
+    <t>0.9999999999999982</t>
+  </si>
+  <si>
     <t>international_law</t>
   </si>
   <si>
@@ -126,6 +132,9 @@
   </si>
   <si>
     <t>112.89999999999999</t>
+  </si>
+  <si>
+    <t>us_foreign_policy</t>
   </si>
   <si>
     <t>high_school_biology first 100</t>
@@ -150,19 +159,13 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color theme="1"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -641,137 +644,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -780,9 +783,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1315,7 +1315,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultColWidth="9.22727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="35.3636363636364" customWidth="1"/>
@@ -1403,7 +1403,7 @@
       <c r="I5">
         <v>7</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="1">
@@ -1449,7 +1449,7 @@
       <c r="I7">
         <v>7</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="K7" s="2">
@@ -1526,7 +1526,7 @@
       <c r="I12">
         <v>11</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K12" s="2">
@@ -1555,16 +1555,16 @@
       <c r="K13" s="2">
         <v>-20.5</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13">
         <v>8</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13">
         <v>11</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="2">
         <v>30.2999999999999</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="2">
         <v>-6.4</v>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       <c r="I15">
         <v>10</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="2">
@@ -1685,7 +1685,7 @@
       <c r="I20">
         <v>8</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="K20" s="1">
@@ -1708,7 +1708,7 @@
       <c r="I21">
         <v>9</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K21" s="1">
@@ -1731,7 +1731,7 @@
       <c r="I22">
         <v>8</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="K22" s="1">
@@ -1771,13 +1771,13 @@
     </row>
     <row r="26" spans="2:11">
       <c r="B26">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
       </c>
       <c r="E26">
-        <v>13791</v>
+        <v>22428</v>
       </c>
       <c r="H26" t="s">
         <v>5</v>
@@ -1797,110 +1797,54 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>12996</v>
+        <v>22131</v>
       </c>
       <c r="G27" t="s">
         <v>9</v>
       </c>
       <c r="H27">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I27">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K27" s="1">
-        <v>-14.7</v>
-      </c>
-    </row>
-    <row r="28" spans="4:11">
+      <c r="K27" s="2">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7">
       <c r="D28" t="s">
         <v>10</v>
       </c>
-      <c r="E28">
-        <v>11284</v>
-      </c>
+      <c r="E28"/>
       <c r="G28" t="s">
         <v>10</v>
       </c>
-      <c r="H28">
-        <v>15</v>
-      </c>
-      <c r="I28">
-        <v>19</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K28" s="1">
-        <v>-41.3999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="4:11">
+    </row>
+    <row r="29" spans="4:7">
       <c r="D29" t="s">
         <v>12</v>
       </c>
-      <c r="E29">
-        <v>7562</v>
-      </c>
+      <c r="E29"/>
       <c r="G29" t="s">
         <v>12</v>
       </c>
-      <c r="H29">
-        <v>20</v>
-      </c>
-      <c r="I29">
-        <v>18</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K29" s="2">
-        <v>-34.7999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="4:11">
+    </row>
+    <row r="30" spans="4:7">
       <c r="D30" t="s">
         <v>13</v>
       </c>
-      <c r="E30">
-        <v>700</v>
-      </c>
+      <c r="E30"/>
       <c r="G30" t="s">
         <v>13</v>
       </c>
-      <c r="H30">
-        <v>15</v>
-      </c>
-      <c r="I30">
-        <v>26</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K30" s="1">
-        <v>-92.4999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="8:11">
-      <c r="H31">
-        <v>12</v>
-      </c>
-      <c r="I31">
-        <v>29</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="1">
-        <v>-84.8</v>
-      </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
         <v>3</v>
@@ -1908,13 +1852,13 @@
     </row>
     <row r="33" spans="2:11">
       <c r="B33">
-        <v>347</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
         <v>4</v>
       </c>
       <c r="E33">
-        <v>34556</v>
+        <v>13791</v>
       </c>
       <c r="H33" t="s">
         <v>5</v>
@@ -1934,22 +1878,22 @@
         <v>9</v>
       </c>
       <c r="E34">
-        <v>26342</v>
+        <v>12996</v>
       </c>
       <c r="G34" t="s">
         <v>9</v>
       </c>
       <c r="H34">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I34">
-        <v>11</v>
-      </c>
-      <c r="J34" s="1">
-        <v>21.7</v>
+        <v>16</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="K34" s="1">
-        <v>-35</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="35" spans="4:11">
@@ -1957,22 +1901,22 @@
         <v>10</v>
       </c>
       <c r="E35">
-        <v>18391</v>
+        <v>11284</v>
       </c>
       <c r="G35" t="s">
         <v>10</v>
       </c>
       <c r="H35">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I35">
-        <v>12</v>
-      </c>
-      <c r="J35" s="1">
-        <v>29.1</v>
+        <v>19</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="K35" s="1">
-        <v>-44.9999999999999</v>
+        <v>-41.3999999999999</v>
       </c>
     </row>
     <row r="36" spans="4:11">
@@ -1980,22 +1924,22 @@
         <v>12</v>
       </c>
       <c r="E36">
-        <v>9974</v>
+        <v>7562</v>
       </c>
       <c r="G36" t="s">
         <v>12</v>
       </c>
       <c r="H36">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I36">
-        <v>10</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>31</v>
+        <v>18</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="K36" s="2">
-        <v>-32.1999999999999</v>
+        <v>-34.7999999999999</v>
       </c>
     </row>
     <row r="37" spans="4:11">
@@ -2003,30 +1947,56 @@
         <v>13</v>
       </c>
       <c r="E37">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
       </c>
       <c r="H37">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I37">
-        <v>11</v>
-      </c>
-      <c r="J37" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" s="1">
+        <v>-92.4999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="8:11">
+      <c r="H38">
+        <v>12</v>
+      </c>
+      <c r="I38">
+        <v>29</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38" s="1">
+        <v>-84.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
         <v>32</v>
       </c>
-      <c r="K37" s="2">
-        <v>-56.3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40" spans="8:11">
+      <c r="E39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
+      <c r="B40">
+        <v>347</v>
+      </c>
+      <c r="D40" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>34556</v>
+      </c>
       <c r="H40" t="s">
         <v>5</v>
       </c>
@@ -2040,124 +2010,316 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="7:11">
+    <row r="41" spans="4:11">
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41">
+        <v>26342</v>
+      </c>
       <c r="G41" t="s">
         <v>9</v>
       </c>
       <c r="H41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I41">
+        <v>11</v>
+      </c>
+      <c r="J41" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="K41" s="1">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="42" spans="4:11">
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42">
+        <v>18391</v>
+      </c>
+      <c r="G42" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42">
+        <v>9</v>
+      </c>
+      <c r="I42">
+        <v>12</v>
+      </c>
+      <c r="J42" s="1">
+        <v>29.1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>-44.9999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="4:11">
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>9974</v>
+      </c>
+      <c r="G43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43">
+        <v>9</v>
+      </c>
+      <c r="I43">
+        <v>10</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K43" s="2">
+        <v>-32.1999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="4:11">
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44">
+        <v>715</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44">
+        <v>22</v>
+      </c>
+      <c r="I44">
+        <v>11</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K44" s="2">
+        <v>-56.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
+      <c r="B47">
+        <v>347</v>
+      </c>
+      <c r="D47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>11561</v>
+      </c>
+      <c r="H47" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" t="s">
+        <v>6</v>
+      </c>
+      <c r="J47" t="s">
+        <v>7</v>
+      </c>
+      <c r="K47" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="1">
+    </row>
+    <row r="48" spans="4:11">
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>11405</v>
+      </c>
+      <c r="G48" t="s">
+        <v>9</v>
+      </c>
+      <c r="H48">
+        <v>7</v>
+      </c>
+      <c r="I48">
+        <v>9</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="K48" s="1">
+        <v>-9.49999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="4:7">
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49"/>
+      <c r="G49" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="4:7">
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50"/>
+      <c r="G50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="4:7">
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51"/>
+      <c r="G51" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="8:11">
+      <c r="H54" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" t="s">
+        <v>6</v>
+      </c>
+      <c r="J54" t="s">
+        <v>7</v>
+      </c>
+      <c r="K54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="7:11">
+      <c r="G55" t="s">
+        <v>9</v>
+      </c>
+      <c r="H55">
+        <v>9</v>
+      </c>
+      <c r="I55">
+        <v>8</v>
+      </c>
+      <c r="J55" s="1">
         <v>14.1</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K55" s="1">
         <v>-30.7999999999999</v>
       </c>
     </row>
-    <row r="42" spans="7:11">
-      <c r="G42" t="s">
-        <v>34</v>
-      </c>
-      <c r="H42">
+    <row r="56" spans="7:11">
+      <c r="G56" t="s">
+        <v>37</v>
+      </c>
+      <c r="H56">
         <v>13</v>
       </c>
-      <c r="I42">
+      <c r="I56">
         <v>10</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J56" s="1">
         <v>21.0999999999999</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K56" s="1">
         <v>-32.2</v>
       </c>
     </row>
-    <row r="43" spans="7:11">
-      <c r="G43" t="s">
-        <v>35</v>
-      </c>
-      <c r="H43">
+    <row r="57" spans="7:11">
+      <c r="G57" t="s">
+        <v>38</v>
+      </c>
+      <c r="H57">
         <v>16</v>
       </c>
-      <c r="I43">
+      <c r="I57">
         <v>8</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J57" s="1">
         <v>21.5999999999999</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K57" s="1">
         <v>-29.2</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="8:11">
-      <c r="H46" t="s">
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="8:11">
+      <c r="H60" t="s">
         <v>5</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I60" t="s">
         <v>6</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J60" t="s">
         <v>7</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K60" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="7:11">
-      <c r="G47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H47">
+    <row r="61" spans="7:11">
+      <c r="G61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H61">
         <v>4</v>
       </c>
-      <c r="I47">
+      <c r="I61">
         <v>5</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J61" s="1">
         <v>2.09999999999999</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K61" s="1">
         <v>-3.29999999999999</v>
       </c>
     </row>
-    <row r="48" spans="7:11">
-      <c r="G48" t="s">
+    <row r="62" spans="7:11">
+      <c r="G62" t="s">
         <v>10</v>
       </c>
-      <c r="H48">
+      <c r="H62">
         <v>3</v>
       </c>
-      <c r="I48">
+      <c r="I62">
         <v>5</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J62" s="1">
         <v>1.59999999999999</v>
       </c>
-      <c r="K48" s="1">
+      <c r="K62" s="1">
         <v>-3.79999999999999</v>
       </c>
     </row>
-    <row r="49" spans="7:11">
-      <c r="G49" t="s">
+    <row r="63" spans="7:11">
+      <c r="G63" t="s">
         <v>13</v>
       </c>
-      <c r="H49">
+      <c r="H63">
         <v>11</v>
       </c>
-      <c r="I49">
-        <v>9</v>
-      </c>
-      <c r="J49" s="1">
+      <c r="I63">
+        <v>9</v>
+      </c>
+      <c r="J63" s="1">
         <v>50.8</v>
       </c>
-      <c r="K49" s="1">
+      <c r="K63" s="1">
         <v>-28.5</v>
       </c>
     </row>

--- a/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/spec3-test_result.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
   <si>
     <t>problem set size</t>
   </si>
@@ -89,6 +89,9 @@
     <t>45.49999999999999</t>
   </si>
   <si>
+    <t>college_biology_02</t>
+  </si>
+  <si>
     <t>high_school_geography</t>
   </si>
   <si>
@@ -135,18 +138,6 @@
   </si>
   <si>
     <t>us_foreign_policy</t>
-  </si>
-  <si>
-    <t>high_school_biology first 100</t>
-  </si>
-  <si>
-    <t>bm100_0</t>
-  </si>
-  <si>
-    <t>bm100_1</t>
-  </si>
-  <si>
-    <t>high_school_geography first 100</t>
   </si>
 </sst>
 </file>
@@ -1315,7 +1306,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultColWidth="9.22727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="35.3636363636364" customWidth="1"/>
@@ -1533,7 +1524,7 @@
         <v>-10.5999999999999</v>
       </c>
     </row>
-    <row r="13" spans="4:15">
+    <row r="13" spans="4:11">
       <c r="D13" t="s">
         <v>9</v>
       </c>
@@ -1554,18 +1545,6 @@
       </c>
       <c r="K13" s="2">
         <v>-20.5</v>
-      </c>
-      <c r="L13">
-        <v>8</v>
-      </c>
-      <c r="M13">
-        <v>11</v>
-      </c>
-      <c r="N13" s="2">
-        <v>30.2999999999999</v>
-      </c>
-      <c r="O13" s="2">
-        <v>-6.4</v>
       </c>
     </row>
     <row r="14" spans="4:11">
@@ -1638,7 +1617,7 @@
       </c>
     </row>
     <row r="17" customHeight="1"/>
-    <row r="18" spans="1:5">
+    <row r="18" customHeight="1" spans="1:5">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1646,15 +1625,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" customHeight="1" spans="2:11">
       <c r="B19">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
       </c>
       <c r="E19">
-        <v>22475</v>
+        <v>16479</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
@@ -1669,101 +1648,60 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="4:11">
+    <row r="20" customHeight="1" spans="4:11">
       <c r="D20" t="s">
         <v>9</v>
       </c>
       <c r="E20">
-        <v>21961</v>
+        <v>13976</v>
       </c>
       <c r="G20" t="s">
         <v>9</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="1">
-        <v>-12.7999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="4:11">
+        <v>11</v>
+      </c>
+      <c r="J20" s="2">
+        <v>30.2999999999999</v>
+      </c>
+      <c r="K20" s="2">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="4:7">
       <c r="D21" t="s">
         <v>10</v>
       </c>
-      <c r="E21">
-        <v>20804</v>
-      </c>
+      <c r="E21"/>
       <c r="G21" t="s">
         <v>10</v>
       </c>
-      <c r="H21">
-        <v>3</v>
-      </c>
-      <c r="I21">
-        <v>9</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K21" s="1">
-        <v>-20.9999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="4:11">
+    </row>
+    <row r="22" customHeight="1" spans="4:7">
       <c r="D22" t="s">
         <v>12</v>
       </c>
-      <c r="E22">
-        <v>16174</v>
-      </c>
+      <c r="E22"/>
       <c r="G22" t="s">
         <v>12</v>
       </c>
-      <c r="H22">
-        <v>4</v>
-      </c>
-      <c r="I22">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="1">
-        <v>-32.5</v>
-      </c>
-    </row>
-    <row r="23" spans="4:11">
+    </row>
+    <row r="23" customHeight="1" spans="4:7">
       <c r="D23" t="s">
         <v>13</v>
       </c>
-      <c r="E23">
-        <v>1170</v>
-      </c>
+      <c r="E23"/>
       <c r="G23" t="s">
         <v>13</v>
       </c>
-      <c r="H23">
-        <v>9</v>
-      </c>
-      <c r="I23">
-        <v>11</v>
-      </c>
-      <c r="J23" s="2">
-        <v>38.4</v>
-      </c>
-      <c r="K23" s="2">
-        <v>-29.7</v>
-      </c>
-    </row>
+    </row>
+    <row r="24" customHeight="1"/>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
         <v>3</v>
@@ -1777,7 +1715,7 @@
         <v>4</v>
       </c>
       <c r="E26">
-        <v>22428</v>
+        <v>22475</v>
       </c>
       <c r="H26" t="s">
         <v>5</v>
@@ -1797,54 +1735,96 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>22131</v>
+        <v>21961</v>
       </c>
       <c r="G27" t="s">
         <v>9</v>
       </c>
       <c r="H27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>6</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" s="2">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="28" spans="4:7">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="1">
+        <v>-12.7999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="4:11">
       <c r="D28" t="s">
         <v>10</v>
       </c>
-      <c r="E28"/>
+      <c r="E28">
+        <v>20804</v>
+      </c>
       <c r="G28" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="4:7">
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28">
+        <v>9</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="1">
+        <v>-20.9999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="4:11">
       <c r="D29" t="s">
         <v>12</v>
       </c>
-      <c r="E29"/>
+      <c r="E29">
+        <v>16174</v>
+      </c>
       <c r="G29" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="4:7">
+      <c r="H29">
+        <v>4</v>
+      </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="1">
+        <v>-32.5</v>
+      </c>
+    </row>
+    <row r="30" spans="4:11">
       <c r="D30" t="s">
         <v>13</v>
       </c>
-      <c r="E30"/>
+      <c r="E30">
+        <v>1170</v>
+      </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
+      <c r="H30">
+        <v>9</v>
+      </c>
+      <c r="I30">
+        <v>11</v>
+      </c>
+      <c r="J30" s="2">
+        <v>38.4</v>
+      </c>
+      <c r="K30" s="2">
+        <v>-29.7</v>
+      </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
         <v>3</v>
@@ -1852,13 +1832,13 @@
     </row>
     <row r="33" spans="2:11">
       <c r="B33">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="D33" t="s">
         <v>4</v>
       </c>
       <c r="E33">
-        <v>13791</v>
+        <v>22428</v>
       </c>
       <c r="H33" t="s">
         <v>5</v>
@@ -1878,110 +1858,51 @@
         <v>9</v>
       </c>
       <c r="E34">
-        <v>12996</v>
+        <v>22131</v>
       </c>
       <c r="G34" t="s">
         <v>9</v>
       </c>
       <c r="H34">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I34">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K34" s="1">
-        <v>-14.7</v>
-      </c>
-    </row>
-    <row r="35" spans="4:11">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7">
       <c r="D35" t="s">
         <v>10</v>
       </c>
-      <c r="E35">
-        <v>11284</v>
-      </c>
       <c r="G35" t="s">
         <v>10</v>
       </c>
-      <c r="H35">
-        <v>15</v>
-      </c>
-      <c r="I35">
-        <v>19</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K35" s="1">
-        <v>-41.3999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="4:11">
+    </row>
+    <row r="36" spans="4:7">
       <c r="D36" t="s">
         <v>12</v>
       </c>
-      <c r="E36">
-        <v>7562</v>
-      </c>
       <c r="G36" t="s">
         <v>12</v>
       </c>
-      <c r="H36">
-        <v>20</v>
-      </c>
-      <c r="I36">
-        <v>18</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K36" s="2">
-        <v>-34.7999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="4:11">
+    </row>
+    <row r="37" spans="4:7">
       <c r="D37" t="s">
         <v>13</v>
       </c>
-      <c r="E37">
-        <v>700</v>
-      </c>
       <c r="G37" t="s">
         <v>13</v>
       </c>
-      <c r="H37">
-        <v>15</v>
-      </c>
-      <c r="I37">
-        <v>26</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K37" s="1">
-        <v>-92.4999999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="8:11">
-      <c r="H38">
-        <v>12</v>
-      </c>
-      <c r="I38">
-        <v>29</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K38" s="1">
-        <v>-84.8</v>
-      </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E39" t="s">
         <v>3</v>
@@ -1989,13 +1910,13 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40">
-        <v>347</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
         <v>4</v>
       </c>
       <c r="E40">
-        <v>34556</v>
+        <v>13791</v>
       </c>
       <c r="H40" t="s">
         <v>5</v>
@@ -2015,22 +1936,22 @@
         <v>9</v>
       </c>
       <c r="E41">
-        <v>26342</v>
+        <v>12996</v>
       </c>
       <c r="G41" t="s">
         <v>9</v>
       </c>
       <c r="H41">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I41">
-        <v>11</v>
-      </c>
-      <c r="J41" s="1">
-        <v>21.7</v>
+        <v>16</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="K41" s="1">
-        <v>-35</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="42" spans="4:11">
@@ -2038,22 +1959,22 @@
         <v>10</v>
       </c>
       <c r="E42">
-        <v>18391</v>
+        <v>11284</v>
       </c>
       <c r="G42" t="s">
         <v>10</v>
       </c>
       <c r="H42">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I42">
-        <v>12</v>
-      </c>
-      <c r="J42" s="1">
-        <v>29.1</v>
+        <v>19</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="K42" s="1">
-        <v>-44.9999999999999</v>
+        <v>-41.3999999999999</v>
       </c>
     </row>
     <row r="43" spans="4:11">
@@ -2061,22 +1982,22 @@
         <v>12</v>
       </c>
       <c r="E43">
-        <v>9974</v>
+        <v>7562</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
       </c>
       <c r="H43">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I43">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K43" s="2">
-        <v>-32.1999999999999</v>
+        <v>-34.7999999999999</v>
       </c>
     </row>
     <row r="44" spans="4:11">
@@ -2084,27 +2005,41 @@
         <v>13</v>
       </c>
       <c r="E44">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
       </c>
       <c r="H44">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I44">
-        <v>11</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K44" s="2">
-        <v>-56.3</v>
+        <v>26</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="1">
+        <v>-92.4999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="8:11">
+      <c r="H45">
+        <v>12</v>
+      </c>
+      <c r="I45">
+        <v>29</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="1">
+        <v>-84.8</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E46" t="s">
         <v>3</v>
@@ -2118,7 +2053,7 @@
         <v>4</v>
       </c>
       <c r="E47">
-        <v>11561</v>
+        <v>34556</v>
       </c>
       <c r="H47" t="s">
         <v>5</v>
@@ -2138,57 +2073,111 @@
         <v>9</v>
       </c>
       <c r="E48">
-        <v>11405</v>
+        <v>26342</v>
       </c>
       <c r="G48" t="s">
         <v>9</v>
       </c>
       <c r="H48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I48">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J48" s="1">
-        <v>1.3</v>
+        <v>21.7</v>
       </c>
       <c r="K48" s="1">
-        <v>-9.49999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="4:7">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="49" spans="4:11">
       <c r="D49" t="s">
         <v>10</v>
       </c>
-      <c r="E49"/>
+      <c r="E49">
+        <v>18391</v>
+      </c>
       <c r="G49" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="4:7">
+      <c r="H49">
+        <v>9</v>
+      </c>
+      <c r="I49">
+        <v>12</v>
+      </c>
+      <c r="J49" s="1">
+        <v>29.1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>-44.9999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="4:11">
       <c r="D50" t="s">
         <v>12</v>
       </c>
-      <c r="E50"/>
+      <c r="E50">
+        <v>9974</v>
+      </c>
       <c r="G50" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="51" spans="4:7">
+      <c r="H50">
+        <v>9</v>
+      </c>
+      <c r="I50">
+        <v>10</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K50" s="2">
+        <v>-32.1999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="4:11">
       <c r="D51" t="s">
         <v>13</v>
       </c>
-      <c r="E51"/>
+      <c r="E51">
+        <v>715</v>
+      </c>
       <c r="G51" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="H51">
+        <v>22</v>
+      </c>
+      <c r="I51">
+        <v>11</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K51" s="2">
+        <v>-56.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="54" spans="8:11">
+      <c r="E53" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
+      <c r="B54">
+        <v>347</v>
+      </c>
+      <c r="D54" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54">
+        <v>11561</v>
+      </c>
       <c r="H54" t="s">
         <v>5</v>
       </c>
@@ -2202,125 +2191,51 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="7:11">
+    <row r="55" spans="4:11">
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55">
+        <v>11405</v>
+      </c>
       <c r="G55" t="s">
         <v>9</v>
       </c>
       <c r="H55">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I55">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J55" s="1">
-        <v>14.1</v>
+        <v>1.3</v>
       </c>
       <c r="K55" s="1">
-        <v>-30.7999999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="7:11">
+        <v>-9.49999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="4:7">
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
       <c r="G56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="4:7">
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="4:7">
+      <c r="D58" t="s">
         <v>13</v>
       </c>
-      <c r="I56">
-        <v>10</v>
-      </c>
-      <c r="J56" s="1">
-        <v>21.0999999999999</v>
-      </c>
-      <c r="K56" s="1">
-        <v>-32.2</v>
-      </c>
-    </row>
-    <row r="57" spans="7:11">
-      <c r="G57" t="s">
-        <v>38</v>
-      </c>
-      <c r="H57">
-        <v>16</v>
-      </c>
-      <c r="I57">
-        <v>8</v>
-      </c>
-      <c r="J57" s="1">
-        <v>21.5999999999999</v>
-      </c>
-      <c r="K57" s="1">
-        <v>-29.2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60" spans="8:11">
-      <c r="H60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I60" t="s">
-        <v>6</v>
-      </c>
-      <c r="J60" t="s">
-        <v>7</v>
-      </c>
-      <c r="K60" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="7:11">
-      <c r="G61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H61">
-        <v>4</v>
-      </c>
-      <c r="I61">
-        <v>5</v>
-      </c>
-      <c r="J61" s="1">
-        <v>2.09999999999999</v>
-      </c>
-      <c r="K61" s="1">
-        <v>-3.29999999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="7:11">
-      <c r="G62" t="s">
-        <v>10</v>
-      </c>
-      <c r="H62">
-        <v>3</v>
-      </c>
-      <c r="I62">
-        <v>5</v>
-      </c>
-      <c r="J62" s="1">
-        <v>1.59999999999999</v>
-      </c>
-      <c r="K62" s="1">
-        <v>-3.79999999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="7:11">
-      <c r="G63" t="s">
+      <c r="G58" t="s">
         <v>13</v>
-      </c>
-      <c r="H63">
-        <v>11</v>
-      </c>
-      <c r="I63">
-        <v>9</v>
-      </c>
-      <c r="J63" s="1">
-        <v>50.8</v>
-      </c>
-      <c r="K63" s="1">
-        <v>-28.5</v>
       </c>
     </row>
   </sheetData>
